--- a/artfynd/A 38875-2019 artfynd.xlsx
+++ b/artfynd/A 38875-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124806412</v>
+        <v>124806672</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -761,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124806672</v>
+        <v>124806412</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,28 +801,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 38875-2019 artfynd.xlsx
+++ b/artfynd/A 38875-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124806672</v>
+        <v>124806412</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -757,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124806412</v>
+        <v>124806672</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,32 +805,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 38875-2019 artfynd.xlsx
+++ b/artfynd/A 38875-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124806412</v>
+        <v>124806672</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -761,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124806672</v>
+        <v>124806412</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,28 +801,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
